--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189280</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189282</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189285</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136189287</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136189288</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136189291</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136189295</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136189307</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189309</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>136189316</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136189322</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189280</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189282</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189285</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136189287</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136189288</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136189291</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136189295</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136189307</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189309</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>136189316</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136189322</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189280</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189282</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189285</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136189287</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136189288</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136189291</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136189295</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136189307</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189309</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>136189316</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136189322</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189280</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189282</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189285</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136189287</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136189288</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136189291</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136189295</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136189307</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189309</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>136189316</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136189322</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189280</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189282</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189285</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136189287</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136189288</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136189291</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136189295</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136189307</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189309</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>136189316</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>136189322</v>
       </c>
       <c r="B21" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 32894-2026 artfynd.xlsx
+++ b/artfynd/A 32894-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189284</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189319</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189281</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189289</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189293</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189294</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189296</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189298</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189304</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136189299</v>
       </c>
       <c r="B22" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136189300</v>
       </c>
       <c r="B23" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136189301</v>
       </c>
       <c r="B24" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>136189302</v>
       </c>
       <c r="B25" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>136189305</v>
       </c>
       <c r="B26" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136189306</v>
       </c>
       <c r="B27" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136189311</v>
       </c>
       <c r="B28" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136189314</v>
       </c>
       <c r="B29" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>136189317</v>
       </c>
       <c r="B30" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136189320</v>
       </c>
       <c r="B31" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>136189321</v>
       </c>
       <c r="B32" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136189323</v>
       </c>
       <c r="B33" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136189324</v>
       </c>
       <c r="B34" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136189325</v>
       </c>
       <c r="B35" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>136189327</v>
       </c>
       <c r="B36" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>136189328</v>
       </c>
       <c r="B37" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>136189329</v>
       </c>
       <c r="B38" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
